--- a/public/downloads/edusad-anketa.xlsx
+++ b/public/downloads/edusad-anketa.xlsx
@@ -173,7 +173,7 @@
     <t>Адрес по-русски *</t>
   </si>
   <si>
-    <t>Улица и дом: г. Актобе, пр. Санкибай батыра, 74</t>
+    <t>Город, улица и дом — с городом сад точно встанет на карту: г. Шымкент, ул. Абая, 12</t>
   </si>
   <si>
     <t>addressKk</t>
